--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6914628-B075-43A0-AADC-93FFE5BD142A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681E7C81-BAB9-4E0E-958C-4BDBD52DC617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="195" windowWidth="37335" windowHeight="19740" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -302,6 +302,11 @@
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
+    <definedName name="Table_CFOA_o">'7.1.1-2 Rice cultivation'!$D$32:$E$38</definedName>
+    <definedName name="Table_E_rice">'7.1.1-2 Rice cultivation'!$D$95:$G$97</definedName>
+    <definedName name="Table_EF_rice_w_p_o">'7.1.1-2 Rice cultivation'!$D$69:$K$71</definedName>
+    <definedName name="Table_ROA_o">'7.1.1-2 Rice cultivation'!$D$23:$J$25</definedName>
+    <definedName name="Table_SF_o">'7.1.1-2 Rice cultivation'!$D$42:$E$44</definedName>
     <definedName name="VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Result_Method1">'7.1.1-2 Rice cultivation'!$E$102</definedName>
     <definedName name="X_Cell_NumberGorwingSeasons">'Input - Rice'!$E$10</definedName>
     <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
@@ -8387,7 +8392,7 @@
         <v>165</v>
       </c>
       <c r="E9" s="114">
-        <f>'7.1.1-2 Rice cultivation'!$E$102</f>
+        <f>VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Result_Method1</f>
         <v>98.450769394817939</v>
       </c>
       <c r="F9" s="114">
@@ -11757,7 +11762,7 @@
         <v>Input</v>
       </c>
       <c r="J91" s="109">
-        <f>'Input - Rice'!E10</f>
+        <f>X_Cell_NumberGorwingSeasons</f>
         <v>2</v>
       </c>
     </row>

--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681E7C81-BAB9-4E0E-958C-4BDBD52DC617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E703FA-A949-4B7B-BE7C-F0A90A85B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -309,6 +309,7 @@
     <definedName name="Table_SF_o">'7.1.1-2 Rice cultivation'!$D$42:$E$44</definedName>
     <definedName name="VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Result_Method1">'7.1.1-2 Rice cultivation'!$E$102</definedName>
     <definedName name="X_Cell_NumberGorwingSeasons">'Input - Rice'!$E$10</definedName>
+    <definedName name="X_Cell_Site_EndDate">'Input - Site'!$E$13</definedName>
     <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
     <definedName name="X_Cell_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Site'!$E$12</definedName>
@@ -16805,21 +16806,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGUAbQBwAGwAbwB5AGUAZAAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAHcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHQAeQBwAGUAXAAiACwAIABcACIAVwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABzAHUAYgAgAC0AIAB0AHkAcABlAFwAIgAsACAAXAAiAFMARgB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHAAbABhAG4AZABcACIALAAgAFwAIgBQAGEAZABkAHkAIAByAG8AdABhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAEYAYQBsAGwAbwB3ACAAdwBpAHQAaABvAHUAdAAgAGYAbABvAG8AZABpAG4AZwAgAGkAbgAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABcACIALAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACAAcABlAHIAaQBvAGQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBSAGUAZwB1AGwAYQByACAAcgBhAGkAbgBmAGUAZABcACIALAAgADAALgA1ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBEAHIAbwB1AGcAaAB0ACAAcAByAG8AbgBlAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIAAwAC4AMAA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAaQBuACAAdABoAGUAIABwAHIAZQAgAC0AIABzAGUAYQBzAG8AbgAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcABlAHIAaQBvAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAAcgBpAG8AcgAgAHQAbwAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAcABcACIALAAgAFwAIgBTAEYAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBjADEAOAAwACAAZABhAHkAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzAFwAIgAsACAAMgAuADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMwA2ADUAIABkAGEAeQBzAFwAIgAsACAAMAAuADUAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAEYATwBBAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgAsACAAXAAiAEMARgBPAEEAaQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABzAGgAbwByAHQAbAB5ACAAKABcAHUAMAAwADMAYwAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADAALgAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABcACIALAAgADAALgAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBhAHIAbQAgAHkAYQByAGQAIABtAGEAbgB1AHIAZQBcACIALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAbQBhAG4AdQByAGUAXAAiACwAIAAwAC4ANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAGMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGEAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQAuADEAOQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQA6ACAAUgBpAGMAZQAgAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuACAAQwBIADQAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAF8AcgBpAGMAZQBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewByAGkAYwBlAH0APQBcAFwAcwB1AG0AXwB3AFwAXABzAHUAbQBfAHAAXABcAHMAdQBtAF8AbwAoAEEAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIAB0AF8AewByAGkAYwBlACwAdwBwAG8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwAgACgAaABhACkAXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAHQAXwByAGkAYwBlAHcAcABvACAAPQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHIAaQBjAGUAdwBwAG8ALAAgAEUARgBfAHIAaQBjAGUAdwBwAG8ALAAgAHQAXwByAGkAYwBlAHcAcABvACwAXABuACAAIAAgACAAUwBVAE0AKABBAF8AcgBpAGMAZQB3AHAAbwAgACoAIABFAEYAXwByAGkAYwBlAHcAcABvACAAKgAgAHQAXwByAGkAYwBlAHcAcABvACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AcgBpAGMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHIAaQBjAGUAdwBwAG8AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABhAHIAZQBhACAAbwBmACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdwAsACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAAsACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABjAG8AbgBkAGkAdABpAG8AbgAgAG8AXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB0AF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZAAgAGYAbwByACAAcgBpAGMAZQAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHMAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAHIAbwBwAHAAaQBuAGcAIABzAGUAYQBzAG8AbgBzACAAaQBuACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAG0AYQBuAGEAZwBlAGQAIAB0AGgAaQBzACAAdwBhAHkAXAAiACwAIABcACIAcwBlAGEAcwBvAG4AcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AG4AdQBtAGIAZQByACAAbwBmACAAcwBlAGEAcwBvAG4AcwBcAHUAMAAwADIANwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAXAB1ADAAMAAyADcAVwBoAGUAcgBlACAAdABoAGUAcgBlACAAaQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIABvAG4AZQAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuACAAcABlAHIAIAB5AGUAYQByACwAIABBAHIAaQBjAGUALAB3AHAAbwAgAHMAaABhAGwAbAAgAGIAZQAgAHMAYwBhAGwAZQBkACAAYQBjAGMAbwByAGQAaQBuAGcAbAB5AFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AXABuAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXABuAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAbgBFAEYAXwBjACAAPQAgAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQApAFwAbgBTAEYAXwB3ACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBwACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXABuAFMARgBfAG8AIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABzAGUAdAAgAHQAbwAgADEAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHUAcwBlACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAEYAXwBjACwAIABTAEYAXwB3ACwAIABTAEYAXwBwACwAIABTAEYAXwBvACwAXABuACAAIAAgACAARQBGAF8AYwAgACoAIABTAEYAXwB3ACAAKgAgAFMARgBfAHAAIAAqACAAUwBGAF8AbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwB3AFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHAAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBvAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA3AC4AMQAuADEALgAxACwAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdwBcACIALAAgAFwAIgB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcAG4AUwBGAF8AbwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AKABSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAKQBeAHsAMAAuADUAOQB9AFwAbgBSAE8AQQBfAG8AIAA9ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AIAAoAHQAbwBuAG4AZQBzAC8AaABhACkAXABuAEMARgBPAEEAXwBvACAAPQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAsACAAQwBGAE8AQQBfAG8ALABcAG4AIAAgACAAIAAoADEAIAArACAAUwBVAE0AKABSAE8AQQBfAG8AIAAqACAAQwBGAE8AQQBfAG8AKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvADEALAAgAEMARgBPAEEAXwBvADEALAAgAFIATwBBAF8AbwAyACwAIABDAEYATwBBAF8AbwAyACwAIABSAE8AQQBfAG8AMwAsACAAQwBGAE8AQQBfAG8AMwAsACAAUgBPAEEAXwBvADQALAAgAEMARgBPAEEAXwBvADQALAAgAFIATwBBAF8AbwA1ACwAIABDAEYATwBBAF8AbwA1ACwAIABSAE8AQQBfAG8ANgAsACAAQwBGAE8AQQBfAG8ANgAsAFwAbgAgACAAIAAgACgAMQAgACsAIAAoACgAUgBPAEEAXwBvADEAIAAqACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAIAAqACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAIAAqACAAQwBGAE8AQQBfAG8AMwApACsAIAAoAFIATwBBAF8AbwA0ACAAKgAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1ACAAKgAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2ACAAKgAgAEMARgBPAEEAXwBvADYAKQApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAIAAoACgAUgBPAEEAXwBvADEAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMwApACAAKwAgACgAUgBPAEEAXwBvADQAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANgApACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIATwBBAF8AbwBcACIALAAgAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgB0AG8AbgBuAGUAcwAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgBPAEEAXwBvAFwAIgAsACAAXAAiAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAbABhAHIAZQBkACAAZQBhAGMAaAAgAGEAbQBlAG4AZABtAGUAbgB0ACAAcwBlAHAAYQByAGEAdABlAGwAeQAgAHQAbwAgAGEAbABsAG8AdwAgAHMAdQBtAG0AaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAIABpAG4AIABvAG4AZQAgAGUAcQB1AGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17014,6 +17000,21 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGUAbQBwAGwAbwB5AGUAZAAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAHcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHQAeQBwAGUAXAAiACwAIABcACIAVwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABzAHUAYgAgAC0AIAB0AHkAcABlAFwAIgAsACAAXAAiAFMARgB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHAAbABhAG4AZABcACIALAAgAFwAIgBQAGEAZABkAHkAIAByAG8AdABhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAEYAYQBsAGwAbwB3ACAAdwBpAHQAaABvAHUAdAAgAGYAbABvAG8AZABpAG4AZwAgAGkAbgAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABcACIALAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACAAcABlAHIAaQBvAGQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBSAGUAZwB1AGwAYQByACAAcgBhAGkAbgBmAGUAZABcACIALAAgADAALgA1ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBEAHIAbwB1AGcAaAB0ACAAcAByAG8AbgBlAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIAAwAC4AMAA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAaQBuACAAdABoAGUAIABwAHIAZQAgAC0AIABzAGUAYQBzAG8AbgAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcABlAHIAaQBvAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAAcgBpAG8AcgAgAHQAbwAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAcABcACIALAAgAFwAIgBTAEYAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBjADEAOAAwACAAZABhAHkAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzAFwAIgAsACAAMgAuADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMwA2ADUAIABkAGEAeQBzAFwAIgAsACAAMAAuADUAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAEYATwBBAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgAsACAAXAAiAEMARgBPAEEAaQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABzAGgAbwByAHQAbAB5ACAAKABcAHUAMAAwADMAYwAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADAALgAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABcACIALAAgADAALgAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBhAHIAbQAgAHkAYQByAGQAIABtAGEAbgB1AHIAZQBcACIALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAbQBhAG4AdQByAGUAXAAiACwAIAAwAC4ANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAGMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGEAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQAuADEAOQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQA6ACAAUgBpAGMAZQAgAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuACAAQwBIADQAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAF8AcgBpAGMAZQBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewByAGkAYwBlAH0APQBcAFwAcwB1AG0AXwB3AFwAXABzAHUAbQBfAHAAXABcAHMAdQBtAF8AbwAoAEEAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIAB0AF8AewByAGkAYwBlACwAdwBwAG8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwAgACgAaABhACkAXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAHQAXwByAGkAYwBlAHcAcABvACAAPQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHIAaQBjAGUAdwBwAG8ALAAgAEUARgBfAHIAaQBjAGUAdwBwAG8ALAAgAHQAXwByAGkAYwBlAHcAcABvACwAXABuACAAIAAgACAAUwBVAE0AKABBAF8AcgBpAGMAZQB3AHAAbwAgACoAIABFAEYAXwByAGkAYwBlAHcAcABvACAAKgAgAHQAXwByAGkAYwBlAHcAcABvACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AcgBpAGMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHIAaQBjAGUAdwBwAG8AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABhAHIAZQBhACAAbwBmACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdwAsACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAAsACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABjAG8AbgBkAGkAdABpAG8AbgAgAG8AXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB0AF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZAAgAGYAbwByACAAcgBpAGMAZQAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHMAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAHIAbwBwAHAAaQBuAGcAIABzAGUAYQBzAG8AbgBzACAAaQBuACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAG0AYQBuAGEAZwBlAGQAIAB0AGgAaQBzACAAdwBhAHkAXAAiACwAIABcACIAcwBlAGEAcwBvAG4AcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AG4AdQBtAGIAZQByACAAbwBmACAAcwBlAGEAcwBvAG4AcwBcAHUAMAAwADIANwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAXAB1ADAAMAAyADcAVwBoAGUAcgBlACAAdABoAGUAcgBlACAAaQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIABvAG4AZQAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuACAAcABlAHIAIAB5AGUAYQByACwAIABBAHIAaQBjAGUALAB3AHAAbwAgAHMAaABhAGwAbAAgAGIAZQAgAHMAYwBhAGwAZQBkACAAYQBjAGMAbwByAGQAaQBuAGcAbAB5AFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AXABuAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXABuAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAbgBFAEYAXwBjACAAPQAgAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQApAFwAbgBTAEYAXwB3ACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBwACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXABuAFMARgBfAG8AIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABzAGUAdAAgAHQAbwAgADEAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHUAcwBlACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAEYAXwBjACwAIABTAEYAXwB3ACwAIABTAEYAXwBwACwAIABTAEYAXwBvACwAXABuACAAIAAgACAARQBGAF8AYwAgACoAIABTAEYAXwB3ACAAKgAgAFMARgBfAHAAIAAqACAAUwBGAF8AbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwB3AFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHAAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBvAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA3AC4AMQAuADEALgAxACwAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdwBcACIALAAgAFwAIgB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcAG4AUwBGAF8AbwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AKABSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAKQBeAHsAMAAuADUAOQB9AFwAbgBSAE8AQQBfAG8AIAA9ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AIAAoAHQAbwBuAG4AZQBzAC8AaABhACkAXABuAEMARgBPAEEAXwBvACAAPQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAsACAAQwBGAE8AQQBfAG8ALABcAG4AIAAgACAAIAAoADEAIAArACAAUwBVAE0AKABSAE8AQQBfAG8AIAAqACAAQwBGAE8AQQBfAG8AKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvADEALAAgAEMARgBPAEEAXwBvADEALAAgAFIATwBBAF8AbwAyACwAIABDAEYATwBBAF8AbwAyACwAIABSAE8AQQBfAG8AMwAsACAAQwBGAE8AQQBfAG8AMwAsACAAUgBPAEEAXwBvADQALAAgAEMARgBPAEEAXwBvADQALAAgAFIATwBBAF8AbwA1ACwAIABDAEYATwBBAF8AbwA1ACwAIABSAE8AQQBfAG8ANgAsACAAQwBGAE8AQQBfAG8ANgAsAFwAbgAgACAAIAAgACgAMQAgACsAIAAoACgAUgBPAEEAXwBvADEAIAAqACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAIAAqACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAIAAqACAAQwBGAE8AQQBfAG8AMwApACsAIAAoAFIATwBBAF8AbwA0ACAAKgAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1ACAAKgAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2ACAAKgAgAEMARgBPAEEAXwBvADYAKQApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAIAAoACgAUgBPAEEAXwBvADEAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMwApACAAKwAgACgAUgBPAEEAXwBvADQAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANgApACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIATwBBAF8AbwBcACIALAAgAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgB0AG8AbgBuAGUAcwAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgBPAEEAXwBvAFwAIgAsACAAXAAiAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAbABhAHIAZQBkACAAZQBhAGMAaAAgAGEAbQBlAG4AZABtAGUAbgB0ACAAcwBlAHAAYQByAGEAdABlAGwAeQAgAHQAbwAgAGEAbABsAG8AdwAgAHMAdQBtAG0AaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAIABpAG4AIABvAG4AZQAgAGUAcQB1AGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
@@ -17023,9 +17024,20 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17042,20 +17054,9 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E703FA-A949-4B7B-BE7C-F0A90A85B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCE1B11-4284-4CD7-839F-32BB88E4EED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -194,6 +194,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -299,6 +300,7 @@
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variable">_xlfn.LAMBDA("SFp")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="SourceData_RiceCultivation_BaselineEF_Data">'Constants - Rice cultivation'!$E$49</definedName>
     <definedName name="Step1">#REF!</definedName>
     <definedName name="Step2">#REF!</definedName>
     <definedName name="Step3">#REF!</definedName>
@@ -11300,7 +11302,7 @@
         <v>Constant</v>
       </c>
       <c r="J59" s="109">
-        <f>'Constants - Rice cultivation'!$E$49</f>
+        <f>SourceData_RiceCultivation_BaselineEF_Data</f>
         <v>1.19</v>
       </c>
     </row>
@@ -16797,12 +16799,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17001,14 +17005,12 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17016,9 +17018,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17043,12 +17048,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCE1B11-4284-4CD7-839F-32BB88E4EED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12233A75-6A54-4EBE-B360-7BF4BCA93035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="Input - Rice" sheetId="70" r:id="rId5"/>
     <sheet name="7.1.1-2 Rice cultivation" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="119" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="120" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -2362,126 +2365,6 @@
   <dxfs count="66">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3341,6 +3224,126 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7032,6 +7035,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7121,12 +7144,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6C986F30-D9EC-4803-8DA0-95980EFC62A0}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1B5CCD20-BA54-40F7-95D6-27015A13EF19}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{DB52865D-6F2D-4651-9C10-87FA05E28EDB}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{A0DC5E69-8490-4C56-B62E-667FA2AAAAD4}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7135,16 +7158,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE5A8FF1-51D1-4DC7-A67C-E1BB1D169339}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{4F5B5655-D5EF-42D6-8659-E68D68704DBF}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE7AB944-8934-40CD-9BD0-1EB0965AAF53}" name="Gas">
+    <tableColumn id="1" xr3:uid="{5B6ADEDE-72A2-4434-A710-6F99C839A21E}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BF74DAA5-1727-4598-8BDF-A1FFEAF36797}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{E1C7B3BC-38A3-4BDC-8C47-05BD771C77EA}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7153,7 +7176,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84EB336F-AD27-4469-81D9-D75BF392704A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{9CA76EB1-B278-4B45-B2E2-8FBD09CECC9A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7162,19 +7185,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6FF8E719-A496-4146-95F1-5C74FB0907DF}" name="Gas">
+    <tableColumn id="1" xr3:uid="{B8FECA2B-4224-4C5B-B6AE-B5A67D4E1AA6}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{141A87B3-BDC7-4BC9-86AA-9AEF8E4516F0}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{7F0885E9-B5F3-4455-9C38-A4C6D7E29209}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6EEA02FE-9CA9-42CC-9715-CE1AE379A798}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{12A08BB7-30F2-406E-B54C-166C02F76997}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{63DBA7EA-762D-4502-893E-4F59C65F1D06}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{F87FFD44-C0A1-4528-A748-D8631F719A0C}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D45503ED-E349-402E-BE70-522640844EB2}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{8A0DE45D-E1A8-492B-B48D-F2430944CDBB}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7183,7 +7206,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B64F6EE9-601E-431C-889B-F490F94AAF6D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{886DBFA7-B553-47C2-8AAD-F95911BEE3D6}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7203,52 +7226,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{E3EAE8D7-79F7-4CFF-AA60-81BEB0D1F996}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{A9372061-091D-4928-AFB2-8A4BA910B299}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{90558006-D3B7-45CA-BB08-CBC5FB2D525E}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5AF6B777-E4AD-4E40-8087-8379FC373B6A}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{31536C54-9D90-4BA1-8630-5A5825932E3D}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{814B39B4-EC2D-4AB7-A363-21ED44CE22E3}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C736DFB1-216D-41C0-9BDA-AF1DACA0D28E}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{BD535553-27C5-46D7-A3F9-5A4D1EB33059}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EBC9733B-D9D6-44EF-92E6-EAE63368707E}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{1ECE1DA9-68B2-4DFD-8EE8-4174920C97BA}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{86BD24B4-BCF5-43E4-9791-66486A239A29}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{B05ACDA7-0798-46F2-873E-86928D4A5130}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{04625927-EE66-47A4-9B56-E9FF16A40381}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{626C69DF-D444-471A-B01F-9ACC328776FA}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0B6D7849-AF37-4F92-B3BC-F00F938473A4}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B62717EE-E402-4C65-9B3B-CECA97019C56}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{79B2D447-365C-4E5B-9B46-EB9A6FEABC8F}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{B7B111E4-5D12-4CE7-B930-9AF4AC9B49EB}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{15AE00CB-0DCC-4C76-9A69-811B2102ABD0}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{3CE52AD2-018D-4080-A0A1-263A9E40D990}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{453B192C-DCF9-4759-9B4F-A3C3978C4EAF}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1CF690CD-2483-40FB-8295-ADE5A346C269}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{399D591D-E030-4FE8-8A4D-14B154F55401}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{30F0655A-5275-40E0-952D-379017AC36AD}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7BB2477B-60BA-4ACB-81E8-FD8FE87495FF}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EBCE9A32-4B33-4DD6-8265-270D2A4FD27D}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A47AD04-56FF-4DD7-A870-3813EAA5B320}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BC9E6BE8-24E9-402B-8339-F60B79C87D91}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FE9A6C0E-201D-4A67-8D4D-C6A488CA05EA}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{50DAD049-D8F4-48FE-BE04-2FEEFA7687FC}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3378CC43-2399-435F-A3FE-BB19D039E80F}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{450AC7D4-B82E-4E6A-B8AD-FE4A5B1AF03F}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7257,16 +7280,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0D035090-ADB1-4F10-9C19-A48DE1D5960D}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{FE17EB54-6DFB-450A-8AF1-DBEE4C8B4214}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1ECE3957-9413-4408-BDB8-77552A7231E8}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{B2536DA8-A01B-497E-9AFB-6AC43FCA3923}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{03FFA737-2FA7-48E9-A115-73FA50C9393D}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F5ECA7FF-0084-477C-9D93-4A01FFA7D46A}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7275,7 +7298,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BEF50EEC-58C1-4511-A309-1BA0389F0DBD}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{B5F7E405-CA81-4BD8-95CF-E0540F2B1121}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7283,16 +7306,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCB9DB5A-F79A-4195-A2D3-345C295DFC8A}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{8A1A7035-9354-40FD-B04D-EDA38D9B762D}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{25D74762-0A2D-4400-B824-894D618905BB}" name="MAT">
+    <tableColumn id="2" xr3:uid="{105A3EF9-6C16-4966-81D5-09862DD43B68}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1205EC90-4A04-43FC-A053-69E387CE1D3F}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{D56D927F-1C90-44F3-A8E5-11A057ECA6A6}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A0CC6FD8-F8F6-4A79-9CDF-BE796852DAF1}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{975BDB72-C35A-4417-8F0B-DD3964173347}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7301,7 +7324,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{356F1A3E-799D-40CF-8D17-7ECCC24A8932}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{B44862CB-547D-4C79-8B2B-B3728B9045A4}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7309,16 +7332,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F2FCA308-B091-442E-94CA-E0A51124F1E1}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{83B12CC1-FA13-41A9-AAED-3C10F9E1FC00}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71D5D2C7-753E-4961-91F7-5D8FD4EBBBB8}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{60964D9D-DE78-4237-889C-50BF70DBE13E}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6FA6F6A2-93E0-4091-A742-AE671B909E65}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{140093AB-6F94-4F6A-ACE4-84323B29A76E}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EBBE1093-D022-42FA-A758-FE815C9D665B}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{6707116B-C084-4FDF-B5E4-21B97667DB76}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7327,16 +7350,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C2C58793-EC57-49E4-811D-88A2C42FD549}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{5FDA09FB-ED11-46B0-B272-76F8715B2110}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8DEDD535-7F20-4744-95AD-A4D8DE59C041}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{76F284D1-91A2-436A-A815-FB97CB398A20}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{413AA76F-C255-42F1-A6D5-5CD24BBBAF26}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{E1E45B7E-7DAC-42AE-90B4-1401B7A9675B}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7345,16 +7368,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{99111242-9C75-4E29-97AB-7B805B522700}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{E339CA29-A79D-4D37-8436-0C10CADF0E46}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BDB9D991-F5EB-4B03-9F51-46A4472289C1}" name="Data source">
+    <tableColumn id="1" xr3:uid="{6EC8DE10-27A9-4495-BA7D-EE77F1E46990}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{01E97336-A13E-4773-A06E-95DCCDC3855D}" name="Data score">
+    <tableColumn id="2" xr3:uid="{29859CE8-85D5-466B-90BD-46D70810AF31}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7363,16 +7386,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2F5DAA02-E4E8-4624-A2C5-096D1B60A921}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{9B32EF9B-C6B5-4352-A70D-31C4FB4A5292}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1FF542F2-F612-45D7-AC03-2F170C811D2C}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{905BB704-ACC6-4E33-A503-5D0C4A550AA4}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CAF3234F-1744-4CC7-97FB-29E26283D105}" name="FracWET" dataDxfId="31">
+    <tableColumn id="2" xr3:uid="{89C22F15-E895-4E43-BFC4-821553960716}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7405,7 +7428,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7C4B023C-39DC-4A61-B287-ACF14E1CC6BC}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{951843A1-4282-40C3-8798-4D159F3191C0}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7414,19 +7437,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{08E69A42-D0D6-4FBD-91D3-EC4843CB8995}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{E07306F9-46D0-4D92-9A2A-BD76FBAEC09F}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FB6F1229-41A4-4698-ADAF-85A7F3BDC850}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{C0A2BA2E-395A-47F6-9224-695F45698587}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48F26286-FAFA-4819-9AFA-F6ECAE3F6B49}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{E6619451-4FEF-4632-8A5E-6A13E1344697}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{99A2A834-E5E1-4659-9E7A-BC2543C1E44F}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{0D152B08-C547-471E-8A5D-EC3EE262D0A1}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4316727C-0C8D-4A2E-947B-24A6E48379FF}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{43A4DE46-0040-4A9C-A71A-524C13D2E470}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7435,16 +7458,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{8771BEDC-DFB7-49CC-BFDB-089589025B03}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{1B905AF8-7442-4D91-978B-56D006F33390}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0349773D-F8B1-4F20-8D67-02CFFC1D5B01}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{6F6A3832-55DE-4125-875D-4B6191B3B67F}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E1A81332-451C-4F13-819A-08B47B324E1A}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C939F4DE-0F59-49E1-A3BB-53C260AFF779}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7453,16 +7476,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{0B56AF9D-3A20-46F2-9DF6-908E16C583F9}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{DAE5A031-4ED8-4C28-9E13-DD64ED6B3D4D}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{19ECEEA9-A0E2-448E-9242-5EB4612E5A30}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{D1566867-B24F-41EC-B0EA-80309C3ADA27}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D5BC812F-1B20-433B-A220-45B290E585E4}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A9A2172F-9C8E-4D1E-8316-16028DEA9C97}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7471,16 +7494,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{9254172A-1F0A-4DA8-AF3D-FBD2D01D814B}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{7B7FEF41-794C-4183-B9C6-910E11DADF68}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{622EF0B5-08C2-435D-AD90-194AA40AF483}" name="Month">
+    <tableColumn id="1" xr3:uid="{7B63E279-B635-448B-AC71-D014F67999B0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B155342-2AE7-4ACF-A9BA-20CE30CBC6E1}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8E442053-3DDC-4532-BCB2-9764B027B4D3}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7489,7 +7512,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{187B9ADF-B9E3-4BCF-ABE8-F47F94E4CCD2}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{E39397A1-BB5D-4DCF-86B8-7AFFFAE10A13}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7509,52 +7532,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{3E609039-97C4-4729-BC48-B95334FF569D}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{DFC83ECF-C07C-4169-8DB0-0DF56F4C72CE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E18B5A5E-83DE-4F01-B188-8A16EF097844}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{726C5116-65FF-4E2C-BC6B-D69F4EEB0DA6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D36388A3-2885-4653-8CA5-464AC2653131}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{15833662-9FA5-48FE-AB03-649163A2077C}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9C1AA35B-D1B9-4F13-9AFE-E084527288D4}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{136E969B-4DA8-49E9-8C3E-25193D8BC8A6}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AFD6DE-B5F7-4FA0-8661-5137CBBDF314}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FAC85047-FDC1-41B4-823C-47752AF125D2}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5C9AC720-CEA6-4B40-B794-DA1221D8A639}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{2E8C335E-EBFC-4E59-9A1C-E60268864FB2}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{454AD809-4295-4C51-9928-79A9335C5131}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{56796689-7858-45DA-93F9-43227E7A844D}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3B58D073-0610-4780-89E8-72FD5F9DE29F}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{3F988011-B7F3-415C-A97B-06EA12F1DA10}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4054B9BB-77F9-4163-856D-1F02090BD29E}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{B2428A5C-8524-4979-9CC5-5CA67B104ED3}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7761C4A1-7DEB-4A74-ABFE-16C4A40CA65E}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C0E281E5-4F70-4D2C-A5FC-2DA4241F29E7}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8CBEF1D1-4341-4566-AE85-0BAE80513B23}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{F89000C7-C2C7-4D49-B28F-81E1D9065BB3}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8AC3B56F-0E3B-46E4-881E-4A4C23336DB8}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{D04AFF1E-BFEE-488E-AE0C-247D5DEB1359}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5E2D555B-CCCB-47A0-ABC6-4BBE59B69EB8}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{007627DF-C545-48E9-AD49-06085CE5147D}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{1ABF9296-D829-4357-B8D0-BF198B1CB558}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{4C5D51BA-12F8-4378-9D25-4CC57D029073}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{143C946F-C17F-411D-99BA-FB5337573E30}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{9718B3A4-6715-4DF9-BD33-7C3C197DE153}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{6876FAEC-5772-4EAC-8F56-60AF713901CD}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{0B888B6F-22AD-43F0-9C31-334EDEBFBB2E}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7563,16 +7586,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{462A48A5-6B2F-4D2D-8025-572DAB9FE02B}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{31E78170-4720-43BA-BF67-2A79A1F89B11}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9C964A67-F781-4D99-8B91-5BFC8B5214FC}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{0978B3C3-B6C5-47DD-8EE2-37EBE246948F}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC008960-0F7E-4D6F-90B0-1B33D47696C5}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2D867627-B7DA-42EC-9FBF-9A7C23808777}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7681,20 +7704,20 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C2292D7-9159-4DA8-868F-97A60010C689}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B4DB5C43-3D9D-4CFB-984A-346252783345}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{556CCF88-C654-4845-97D7-9D7D362BCE69}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{441CEB72-C4DE-48A9-8DEE-57051EAB0C9C}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{281E9821-9727-41EE-9BB2-A0EE34626517}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{D9201134-D504-4EF7-ABD9-14A69F3640F7}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB9ED2A9-4530-4389-9F51-62F4D51CBA86}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{69AFD6AF-AC75-4ADE-9F72-18F49E6F640E}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10544,62 +10567,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12807,7 +12830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE7628F-C552-4DBE-BEDA-1D3AB479C827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DA982F3-9319-4778-A641-7A453B54559B}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16799,14 +16822,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17005,25 +17026,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGUAbQBwAGwAbwB5AGUAZAAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAHcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHQAeQBwAGUAXAAiACwAIABcACIAVwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABzAHUAYgAgAC0AIAB0AHkAcABlAFwAIgAsACAAXAAiAFMARgB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHAAbABhAG4AZABcACIALAAgAFwAIgBQAGEAZABkAHkAIAByAG8AdABhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAEYAYQBsAGwAbwB3ACAAdwBpAHQAaABvAHUAdAAgAGYAbABvAG8AZABpAG4AZwAgAGkAbgAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABcACIALAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACAAcABlAHIAaQBvAGQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBSAGUAZwB1AGwAYQByACAAcgBhAGkAbgBmAGUAZABcACIALAAgADAALgA1ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBEAHIAbwB1AGcAaAB0ACAAcAByAG8AbgBlAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIAAwAC4AMAA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAaQBuACAAdABoAGUAIABwAHIAZQAgAC0AIABzAGUAYQBzAG8AbgAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcABlAHIAaQBvAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAAcgBpAG8AcgAgAHQAbwAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAcABcACIALAAgAFwAIgBTAEYAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBjADEAOAAwACAAZABhAHkAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzAFwAIgAsACAAMgAuADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMwA2ADUAIABkAGEAeQBzAFwAIgAsACAAMAAuADUAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAEYATwBBAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgAsACAAXAAiAEMARgBPAEEAaQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABzAGgAbwByAHQAbAB5ACAAKABcAHUAMAAwADMAYwAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADAALgAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABcACIALAAgADAALgAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBhAHIAbQAgAHkAYQByAGQAIABtAGEAbgB1AHIAZQBcACIALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAbQBhAG4AdQByAGUAXAAiACwAIAAwAC4ANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAGMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGEAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQAuADEAOQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQA6ACAAUgBpAGMAZQAgAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuACAAQwBIADQAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAF8AcgBpAGMAZQBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewByAGkAYwBlAH0APQBcAFwAcwB1AG0AXwB3AFwAXABzAHUAbQBfAHAAXABcAHMAdQBtAF8AbwAoAEEAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIAB0AF8AewByAGkAYwBlACwAdwBwAG8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwAgACgAaABhACkAXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAHQAXwByAGkAYwBlAHcAcABvACAAPQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHIAaQBjAGUAdwBwAG8ALAAgAEUARgBfAHIAaQBjAGUAdwBwAG8ALAAgAHQAXwByAGkAYwBlAHcAcABvACwAXABuACAAIAAgACAAUwBVAE0AKABBAF8AcgBpAGMAZQB3AHAAbwAgACoAIABFAEYAXwByAGkAYwBlAHcAcABvACAAKgAgAHQAXwByAGkAYwBlAHcAcABvACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AcgBpAGMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHIAaQBjAGUAdwBwAG8AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABhAHIAZQBhACAAbwBmACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdwAsACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAAsACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABjAG8AbgBkAGkAdABpAG8AbgAgAG8AXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB0AF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZAAgAGYAbwByACAAcgBpAGMAZQAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHMAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAHIAbwBwAHAAaQBuAGcAIABzAGUAYQBzAG8AbgBzACAAaQBuACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAG0AYQBuAGEAZwBlAGQAIAB0AGgAaQBzACAAdwBhAHkAXAAiACwAIABcACIAcwBlAGEAcwBvAG4AcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AG4AdQBtAGIAZQByACAAbwBmACAAcwBlAGEAcwBvAG4AcwBcAHUAMAAwADIANwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAXAB1ADAAMAAyADcAVwBoAGUAcgBlACAAdABoAGUAcgBlACAAaQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIABvAG4AZQAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuACAAcABlAHIAIAB5AGUAYQByACwAIABBAHIAaQBjAGUALAB3AHAAbwAgAHMAaABhAGwAbAAgAGIAZQAgAHMAYwBhAGwAZQBkACAAYQBjAGMAbwByAGQAaQBuAGcAbAB5AFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AXABuAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXABuAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAbgBFAEYAXwBjACAAPQAgAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQApAFwAbgBTAEYAXwB3ACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBwACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXABuAFMARgBfAG8AIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABzAGUAdAAgAHQAbwAgADEAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHUAcwBlACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAEYAXwBjACwAIABTAEYAXwB3ACwAIABTAEYAXwBwACwAIABTAEYAXwBvACwAXABuACAAIAAgACAARQBGAF8AYwAgACoAIABTAEYAXwB3ACAAKgAgAFMARgBfAHAAIAAqACAAUwBGAF8AbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwB3AFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHAAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBvAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA3AC4AMQAuADEALgAxACwAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdwBcACIALAAgAFwAIgB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcAG4AUwBGAF8AbwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AKABSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAKQBeAHsAMAAuADUAOQB9AFwAbgBSAE8AQQBfAG8AIAA9ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AIAAoAHQAbwBuAG4AZQBzAC8AaABhACkAXABuAEMARgBPAEEAXwBvACAAPQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAsACAAQwBGAE8AQQBfAG8ALABcAG4AIAAgACAAIAAoADEAIAArACAAUwBVAE0AKABSAE8AQQBfAG8AIAAqACAAQwBGAE8AQQBfAG8AKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvADEALAAgAEMARgBPAEEAXwBvADEALAAgAFIATwBBAF8AbwAyACwAIABDAEYATwBBAF8AbwAyACwAIABSAE8AQQBfAG8AMwAsACAAQwBGAE8AQQBfAG8AMwAsACAAUgBPAEEAXwBvADQALAAgAEMARgBPAEEAXwBvADQALAAgAFIATwBBAF8AbwA1ACwAIABDAEYATwBBAF8AbwA1ACwAIABSAE8AQQBfAG8ANgAsACAAQwBGAE8AQQBfAG8ANgAsAFwAbgAgACAAIAAgACgAMQAgACsAIAAoACgAUgBPAEEAXwBvADEAIAAqACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAIAAqACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAIAAqACAAQwBGAE8AQQBfAG8AMwApACsAIAAoAFIATwBBAF8AbwA0ACAAKgAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1ACAAKgAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2ACAAKgAgAEMARgBPAEEAXwBvADYAKQApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAIAAoACgAUgBPAEEAXwBvADEAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMwApACAAKwAgACgAUgBPAEEAXwBvADQAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANgApACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIATwBBAF8AbwBcACIALAAgAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgB0AG8AbgBuAGUAcwAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgBPAEEAXwBvAFwAIgAsACAAXAAiAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAbABhAHIAZQBkACAAZQBhAGMAaAAgAGEAbQBlAG4AZABtAGUAbgB0ACAAcwBlAHAAYQByAGEAdABlAGwAeQAgAHQAbwAgAGEAbABsAG8AdwAgAHMAdQBtAG0AaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAIABpAG4AIABvAG4AZQAgAGUAcQB1AGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17048,9 +17068,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12233A75-6A54-4EBE-B360-7BF4BCA93035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B9F757-DE34-4861-8FED-78E131A4FA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
     <sheet name="Constants - Common" sheetId="120" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -56,7 +53,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -72,9 +79,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -285,7 +311,13 @@
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Unit">_xlfn.LAMBDA("kg CH4 / ha / day")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Variable">_xlfn.LAMBDA("EFc")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Organic amendment i","CFOAi";"Straw incorporated shortly (&lt;30 days) before cultivation",1;"Straw incorporated long (&gt;30 days) before cultivation",0.19;"Compost",0.17;"Farm yard manure",0.21;"Green manure",0.45;"Inorganic fertiliser",1}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(7, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Organic amendment i","CFOAi";"Straw incorporated shortly (&lt;30 days) before cultivation",1;"Straw incorporated long (&gt;30 days) before cultivation",0.19;"Compost",0.17;"Farm yard manure",0.21;"Green manure",0.45;"Inorganic fertiliser",1}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.3.3")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Title">_xlfn.LAMBDA("Conversion factor for organic amendment i")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -2365,6 +2397,126 @@
   <dxfs count="66">
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3224,126 +3376,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7035,26 +7067,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7133,7 +7145,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FE260FFD-8165-44FA-8171-CF7DA9E6EDC2}" name="Amendment mix name"/>
     <tableColumn id="2" xr3:uid="{1656D970-5568-46C3-8CF9-6544B58E60EE}" name="Straw added &lt; 30 days precultivation (t/ha)"/>
-    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days pre cultivation (t/ha)" dataDxfId="53" dataCellStyle="Content normal"/>
+    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days pre cultivation (t/ha)" dataDxfId="17" dataCellStyle="Content normal"/>
     <tableColumn id="3" xr3:uid="{7414D722-C23C-43BF-8BE4-9A787F770773}" name="Compost (t/ha)"/>
     <tableColumn id="4" xr3:uid="{10821F0A-FFAB-47C5-A2D8-0C77A91D1E11}" name="Farm yard manure (t/ha)"/>
     <tableColumn id="5" xr3:uid="{7554AF1F-8437-4EC1-A35B-D5ADAFFC9535}" name="Green manure (t/ha)"/>
@@ -7229,49 +7241,49 @@
     <tableColumn id="1" xr3:uid="{A9372061-091D-4928-AFB2-8A4BA910B299}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5AF6B777-E4AD-4E40-8087-8379FC373B6A}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{5AF6B777-E4AD-4E40-8087-8379FC373B6A}" name="MAT" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{814B39B4-EC2D-4AB7-A363-21ED44CE22E3}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{814B39B4-EC2D-4AB7-A363-21ED44CE22E3}" name="MAP" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{BD535553-27C5-46D7-A3F9-5A4D1EB33059}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{BD535553-27C5-46D7-A3F9-5A4D1EB33059}" name="Frost days per year" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1ECE1DA9-68B2-4DFD-8EE8-4174920C97BA}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{1ECE1DA9-68B2-4DFD-8EE8-4174920C97BA}" name="Elevation" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B05ACDA7-0798-46F2-873E-86928D4A5130}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{B05ACDA7-0798-46F2-873E-86928D4A5130}" name="MAP:PET" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{626C69DF-D444-471A-B01F-9ACC328776FA}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{626C69DF-D444-471A-B01F-9ACC328776FA}" name="Min temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B62717EE-E402-4C65-9B3B-CECA97019C56}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{B62717EE-E402-4C65-9B3B-CECA97019C56}" name="Max temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B7B111E4-5D12-4CE7-B930-9AF4AC9B49EB}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{B7B111E4-5D12-4CE7-B930-9AF4AC9B49EB}" name="Min rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3CE52AD2-018D-4080-A0A1-263A9E40D990}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{3CE52AD2-018D-4080-A0A1-263A9E40D990}" name="Max rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{1CF690CD-2483-40FB-8295-ADE5A346C269}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{1CF690CD-2483-40FB-8295-ADE5A346C269}" name="Min frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{30F0655A-5275-40E0-952D-379017AC36AD}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{30F0655A-5275-40E0-952D-379017AC36AD}" name="Max frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{EBCE9A32-4B33-4DD6-8265-270D2A4FD27D}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{EBCE9A32-4B33-4DD6-8265-270D2A4FD27D}" name="Min elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{BC9E6BE8-24E9-402B-8339-F60B79C87D91}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{BC9E6BE8-24E9-402B-8339-F60B79C87D91}" name="Max elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50DAD049-D8F4-48FE-BE04-2FEEFA7687FC}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{50DAD049-D8F4-48FE-BE04-2FEEFA7687FC}" name="Min MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{450AC7D4-B82E-4E6A-B8AD-FE4A5B1AF03F}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{450AC7D4-B82E-4E6A-B8AD-FE4A5B1AF03F}" name="Max MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7289,7 +7301,7 @@
     <tableColumn id="1" xr3:uid="{B2536DA8-A01B-497E-9AFB-6AC43FCA3923}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F5ECA7FF-0084-477C-9D93-4A01FFA7D46A}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{F5ECA7FF-0084-477C-9D93-4A01FFA7D46A}" name="Wet or Dry Zone" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7395,7 +7407,7 @@
     <tableColumn id="1" xr3:uid="{905BB704-ACC6-4E33-A503-5D0C4A550AA4}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{89C22F15-E895-4E43-BFC4-821553960716}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{89C22F15-E895-4E43-BFC4-821553960716}" name="FracWET" dataDxfId="37">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7416,7 +7428,7 @@
   </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6CF21226-E2F8-4356-887C-701D50A69505}" name="Regime name"/>
-    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="52" dataCellStyle="Content normal"/>
+    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="16" dataCellStyle="Content normal"/>
     <tableColumn id="2" xr3:uid="{EA5A5A10-60BF-4C8A-8D3B-469871BE7F8E}" name="Pre-cultivation water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{85A41168-485F-4954-954D-E24F2E46EB1B}" name="Water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{EF7FE10B-862C-4478-9622-5C7E7DA42BCC}" name="Water regime sub-type (select)" dataCellStyle="Input select"/>
@@ -7467,7 +7479,7 @@
     <tableColumn id="1" xr3:uid="{6F6A3832-55DE-4125-875D-4B6191B3B67F}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C939F4DE-0F59-49E1-A3BB-53C260AFF779}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C939F4DE-0F59-49E1-A3BB-53C260AFF779}" name="FracWET" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7485,7 +7497,7 @@
     <tableColumn id="1" xr3:uid="{D1566867-B24F-41EC-B0EA-80309C3ADA27}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A9A2172F-9C8E-4D1E-8316-16028DEA9C97}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{A9A2172F-9C8E-4D1E-8316-16028DEA9C97}" name="EFPRP" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7503,7 +7515,7 @@
     <tableColumn id="1" xr3:uid="{7B63E279-B635-448B-AC71-D014F67999B0}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8E442053-3DDC-4532-BCB2-9764B027B4D3}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{8E442053-3DDC-4532-BCB2-9764B027B4D3}" name="Season" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7535,49 +7547,49 @@
     <tableColumn id="1" xr3:uid="{DFC83ECF-C07C-4169-8DB0-0DF56F4C72CE}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{726C5116-65FF-4E2C-BC6B-D69F4EEB0DA6}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{726C5116-65FF-4E2C-BC6B-D69F4EEB0DA6}" name="MAT (ºC)" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{15833662-9FA5-48FE-AB03-649163A2077C}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{15833662-9FA5-48FE-AB03-649163A2077C}" name="Anaerobic lagoon" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{136E969B-4DA8-49E9-8C3E-25193D8BC8A6}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{136E969B-4DA8-49E9-8C3E-25193D8BC8A6}" name="Digester / covered lagoons" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FAC85047-FDC1-41B4-823C-47752AF125D2}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FAC85047-FDC1-41B4-823C-47752AF125D2}" name="Liquid systems" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2E8C335E-EBFC-4E59-9A1C-E60268864FB2}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{2E8C335E-EBFC-4E59-9A1C-E60268864FB2}" name="Daily spread" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{56796689-7858-45DA-93F9-43227E7A844D}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{56796689-7858-45DA-93F9-43227E7A844D}" name="Composting (passive windrow)" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3F988011-B7F3-415C-A97B-06EA12F1DA10}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{3F988011-B7F3-415C-A97B-06EA12F1DA10}" name="Solid storage" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{B2428A5C-8524-4979-9CC5-5CA67B104ED3}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{B2428A5C-8524-4979-9CC5-5CA67B104ED3}" name="Pit storage" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C0E281E5-4F70-4D2C-A5FC-2DA4241F29E7}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{C0E281E5-4F70-4D2C-A5FC-2DA4241F29E7}" name="Deep litter" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F89000C7-C2C7-4D49-B28F-81E1D9065BB3}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{F89000C7-C2C7-4D49-B28F-81E1D9065BB3}" name="Poultry manure with bedding" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{D04AFF1E-BFEE-488E-AE0C-247D5DEB1359}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{D04AFF1E-BFEE-488E-AE0C-247D5DEB1359}" name="Poultry manure without bedding" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{007627DF-C545-48E9-AD49-06085CE5147D}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{007627DF-C545-48E9-AD49-06085CE5147D}" name="Direct processing" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{4C5D51BA-12F8-4378-9D25-4CC57D029073}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{4C5D51BA-12F8-4378-9D25-4CC57D029073}" name="Direct application" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9718B3A4-6715-4DF9-BD33-7C3C197DE153}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{9718B3A4-6715-4DF9-BD33-7C3C197DE153}" name="Pasture range and paddock" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0B888B6F-22AD-43F0-9C31-334EDEBFBB2E}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{0B888B6F-22AD-43F0-9C31-334EDEBFBB2E}" name="MAT raw" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7595,7 +7607,7 @@
     <tableColumn id="1" xr3:uid="{0978B3C3-B6C5-47DD-8EE2-37EBE246948F}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2D867627-B7DA-42EC-9FBF-9A7C23808777}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2D867627-B7DA-42EC-9FBF-9A7C23808777}" name="EFNi &amp; EFN2Oi" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7614,10 +7626,10 @@
     <tableColumn id="1" xr3:uid="{3A2980B6-3A2D-485C-8340-4AB52CBFBB99}" name="Water regime type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7635,7 +7647,7 @@
     <tableColumn id="1" xr3:uid="{FF0717D8-C262-491B-A316-62679EA1B7D7}" name="Water regime prior to cultivation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7653,7 +7665,7 @@
     <tableColumn id="1" xr3:uid="{4FCCD68A-6FAE-4D17-88E1-28AE833F5E5E}" name="Organic amendment i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10567,62 +10579,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16822,15 +16834,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17025,7 +17028,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -17036,19 +17052,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17067,7 +17071,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17076,12 +17096,4 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8AB70E-3CFF-451A-A195-09073FE646C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D50DF0-286E-431E-BA80-63DF81CC8452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -9544,7 +9544,7 @@
         <v>58</v>
       </c>
       <c r="E13" s="58">
-        <f>DATE(YEAR(E12)+1,MONTH(E12),DAY(E12))-1</f>
+        <f>DATE(YEAR(X_Cell_Site_StartDate)+1,MONTH(X_Cell_Site_StartDate),DAY(X_Cell_Site_StartDate))-1</f>
         <v>45657</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -10492,7 +10492,7 @@
         <v>Rice</v>
       </c>
       <c r="D10" s="1" t="str">
-        <f>"Number of full growing seasons between "&amp;TEXT('Input - Site'!$E$12,"d/m/yy")&amp;" and " &amp; TEXT('Input - Site'!$E$13,"d/m/yy") &amp; " that are managed the same way"</f>
+        <f>"Number of full growing seasons between "&amp;TEXT(X_Cell_Site_StartDate,"d/m/yy")&amp;" and " &amp; TEXT(X_Cell_Site_EndDate,"d/m/yy") &amp; " that are managed the same way"</f>
         <v>Number of full growing seasons between 1/1/24 and 31/12/24 that are managed the same way</v>
       </c>
       <c r="E10" s="104">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="F104" s="87"/>
       <c r="G104" s="46">
-        <f>E102</f>
+        <f>VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Result_Method1</f>
         <v>98.450769394817939</v>
       </c>
     </row>
@@ -17265,6 +17265,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -17273,22 +17277,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17483,7 +17472,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -17491,26 +17499,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17527,4 +17516,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D50DF0-286E-431E-BA80-63DF81CC8452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572800A9-0504-4567-8631-66CFC1DE1562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="36255" windowHeight="19140" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -263,20 +263,6 @@
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
-    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
-    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
-    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
-    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
-    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
-    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation">_xlfn.LAMBDA(_xlpm.A_ricewpo,_xlpm.EF_ricewpo,_xlpm.t_ricewpo, SUM(_xlpm.A_ricewpo * _xlpm.EF_ricewpo * _xlpm.t_ricewpo) * 10 ^ -3)</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"A_ricewpo","annual area of rice cultivation under water regime w, pre-season water regime p, and organic amendment condition o","ha","Input";"EF_ricewpo","emission factor for rice cultivation under conditions w, p, and o","kg CH4/ha/day","Calculated from 7.1.1.1, (2)";"t_ricewpo","cultivation period for rice under conditions w, p, and o","days","Input";"s","number of cropping seasons in reporting period managed this way","seasons","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_LatexEquation">_xlfn.LAMBDA("E_{rice}=\sum_w\sum_p\sum_o(A_{rice,wpo}\times EF_{rice,wpo}\times t_{rice,wpo})\times 10^{-3}")</definedName>
@@ -336,9 +322,6 @@
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variable">_xlfn.LAMBDA("SFp")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variation">_xlfn.LAMBDA("")</definedName>
     <definedName name="SourceData_RiceCultivation_BaselineEF_Data">'Constants - Rice cultivation'!$E$49</definedName>
-    <definedName name="Step1">#REF!</definedName>
-    <definedName name="Step2">#REF!</definedName>
-    <definedName name="Step3">#REF!</definedName>
     <definedName name="Table_CFOA_o">'7.1.1-2 Rice cultivation'!$D$32:$E$38</definedName>
     <definedName name="Table_E_rice">'7.1.1-2 Rice cultivation'!$D$95:$G$97</definedName>
     <definedName name="Table_EF_rice_w_p_o">'7.1.1-2 Rice cultivation'!$D$69:$K$71</definedName>
@@ -17265,10 +17248,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -17277,7 +17256,22 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17472,18 +17466,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
@@ -17491,15 +17482,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17516,15 +17510,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/7_RiceCultivation_WIP_v02.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572800A9-0504-4567-8631-66CFC1DE1562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A9FC37-BEB1-4EDD-8890-6BCE7FB3991D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="36255" windowHeight="19140" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Input - Rice" sheetId="70" r:id="rId5"/>
     <sheet name="7.1.1-2 Rice cultivation" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="121" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="122" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
@@ -141,7 +141,13 @@
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Title">_xlfn.LAMBDA("Emission factor for nitrogen leaching and runoff")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Unit">_xlfn.LAMBDA("(kg N2O-N / kg N")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFleach_Variation">_xlfn.LAMBDA((""))</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(15, 5, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_EFN2O_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(14, 5,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Production system j","EFN2O","Production system only","Irrigation method","Rainfall zone";"Irrigated pasture",0.0059,"Pasture","Any","Any";"Irrigated crop",0.007,"Crop","Any","Any";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","Low rainfall";"Non-irrigated pasture",0.0018,"Pasture","Not irrigated","High rainfall";"Non-irrigated crop (low rainfall)",0.0029,"Crop","Not irrigated","Low rainfall";"Non-irrigated crop (high rainfall)",0.008,"Crop","Not irrigated","High rainfall";"Sugar",0.0199,"Sugar","Any","Any";"Cotton",0.0053,"Cotton","Any","Any";"Horticultural crops",0.0064,"Horticultural crops","Any","Any";"Rice (continuous flooding)",0.003,"Rice","Continuous flooding","Any";"Rice (single and multiple drainage, or alternate wetting and drying)",0.005,"Rice","Single and multiple drainage, or alternate wetting and drying","Any";"Aquaculture",0.0026,"Aquaculture","Any","Any";"Forestry",0.0018,"Forestry","Any","Any"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_NIRReference">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.2.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_EFN2O_Title">_xlfn.LAMBDA("Nitrous oxide emission factors for inorganic fertiliser application")</definedName>
@@ -183,13 +189,25 @@
     <definedName name="Common_SourceData.Common_SourceData_GWP_Title">_xlfn.LAMBDA("Global warming potential for greenhouse gases")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Unit">_xlfn.LAMBDA("factor")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_GWP_Variable">_xlfn.LAMBDA("GWPN2O")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(3, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Leaching Zone","Leaching criteria";"Leaching occurs","Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦";"Leaching does not occur","Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Source">_xlfn.LAMBDA("VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Title">_xlfn.LAMBDA("VEERG Australian leaching zones")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_LeachingZones_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(22, 16, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(21, 16,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Temperature zone","MAT (ºC)","Uncovered anerobic lagoon","Covered lagoon","Liquid Slurry (without natural crust)","Daily spread (b)","Composting (passive windrow)","Solid Storage","Pit Storage &lt;1 month","Deep Litter","Poultry Manure (with/without litter)","","Direct processing into pelletized fertiliser","Direct application to soil","Pasture, Range and Paddock (c)(d)","MAT raw";"Cool","≤10",0.66,0.1,0.1,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,10;"Cool",11,0.68,0.1,0.11,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,11;"Cool",12,0.7,0.1,0.13,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,12;"Cool",13,0.71,0.1,0.14,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,13;"Cool",14,0.73,0.1,0.15,0.001,0.005,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,14;"Temperate",15,0.74,0.1,0.17,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,15;"Temperate",16,0.75,0.1,0.18,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,16;"Temperate",17,0.76,0.1,0.2,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,17;"Temperate",18,0.77,0.1,0.22,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,18;"Temperate",19,0.77,0.1,0.24,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,19;"Temperate",20,0.78,0.1,0.26,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,20;"Temperate",21,0.78,0.1,0.29,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,21;"Temperate",22,0.78,0.1,0.31,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,22;"Temperate",23,0.79,0.1,0.34,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,23;"Temperate",24,0.79,0.1,0.37,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,24;"Temperate",25,0.79,0.1,0.41,0.005,0.01,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,25;"Warm",26,0.79,0.1,0.44,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,26;"Warm",27,0.8,0.1,0.48,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,27;"Warm","≥28",0.8,0.1,0.5,0.01,0.015,0.02,0.03,0.04,0.015,0.015,0,0,0.0047,28;"","","Anaerobic lagoon","Digester / covered lagoons","Liquid systems","Daily spread","Composting (passive windrow)","Solid storage","Pit storage","Deep litter","Poultry manure with bedding","Poultry manure without bedding","Direct processing","Direct application","Pasture range and paddock","MAT raw"}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Source">_xlfn.LAMBDA("VEERG 2026: Table A.1.8.1")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Title">_xlfn.LAMBDA("Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_MCFTemperatureZone_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -260,9 +278,15 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
     <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Enterprise_PastureBeef_InputFunctions.multiplyCorrespondingCells">_xlfn.LAMBDA(_xlpm.range1,_xlpm.range2,_xlpm.range3, _xlfn.LET(_xlpm.numRows, ROWS(_xlpm.range1), _xlpm.numCols, COLUMNS(_xlpm.range1), _xlpm.result, _xlfn.MAKEARRAY(_xlpm.numRows, _xlpm.numCols, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, IF(ISNUMBER(INDEX(_xlpm.range1, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range1, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range2, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range2, _xlpm.r, _xlpm.c), 0) * IF(ISNUMBER(INDEX(_xlpm.range3, _xlpm.r, _xlpm.c)), INDEX(_xlpm.range3, _xlpm.r, _xlpm.c), 0))), _xlpm.result))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="InputFunctions_PastureBeef.ConvertMonthlyCalvingToSeason">_xlfn.LAMBDA(_xlpm.Season,_xlpm.SumArray,_xlpm.CalvingMonthArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.MonthText, TEXT(_xlpm.CalvingMonthArray, "mmmm"), _xlpm.SeasonPerRow, _xlfn.XLOOKUP(_xlpm.MonthText, _xlpm.MonthArray, _xlpm.MonthToSeasonArray, "", 0), SUM(_xlpm.SumArray * (_xlpm.SeasonPerRow = _xlpm.Season))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.Month, TEXT(_xlpm.Month, "mmmm"), _xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(_xlpm.Month, _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupLiveweightFromSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.LivestockClass,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.LivestockClassArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region) * (_xlpm.SeasonArray = _xlpm.Season), _xlfn.XLOOKUP(_xlpm.LivestockClass, _xlpm.LivestockClassArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionMonth">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Month,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray,_xlpm.MonthArray,_xlpm.MonthToSeasonArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlpm.Season, _xlfn.XLOOKUP(TEXT(_xlpm.Month, "mmmm"), _xlpm.MonthArray, _xlpm.MonthToSeasonArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
+    <definedName name="InputFunctions_PastureBeef.LookupValueFromStateRegionSeason">_xlfn.LAMBDA(_xlpm.State,_xlpm.Region,_xlpm.Season,_xlpm.StateArray,_xlpm.RegionArray,_xlpm.SeasonArray,_xlpm.ReturnArray,_xlpm.StateCommonNameArray,_xlpm.StateAbbreviationArray, _xlfn.LET(_xlpm.State, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateCommonNameArray, _xlpm.StateAbbreviationArray), _xlfn.XLOOKUP(1, (_xlpm.StateArray = _xlpm.State) * (_xlpm.RegionArray = _xlpm.Region), _xlfn.XLOOKUP(_xlpm.Season, _xlpm.SeasonArray, _xlpm.ReturnArray))))</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation">_xlfn.LAMBDA(_xlpm.A_ricewpo,_xlpm.EF_ricewpo,_xlpm.t_ricewpo, SUM(_xlpm.A_ricewpo * _xlpm.EF_ricewpo * _xlpm.t_ricewpo) * 10 ^ -3)</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"A_ricewpo","annual area of rice cultivation under water regime w, pre-season water regime p, and organic amendment condition o","ha","Input";"EF_ricewpo","emission factor for rice cultivation under conditions w, p, and o","kg CH4/ha/day","Calculated from 7.1.1.1, (2)";"t_ricewpo","cultivation period for rice under conditions w, p, and o","days","Input";"s","number of cropping seasons in reporting period managed this way","seasons","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_LatexEquation">_xlfn.LAMBDA("E_{rice}=\sum_w\sum_p\sum_o(A_{rice,wpo}\times EF_{rice,wpo}\times t_{rice,wpo})\times 10^{-3}")</definedName>
@@ -392,7 +416,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="219">
   <si>
     <t>INPUTS</t>
   </si>
@@ -1002,6 +1026,153 @@
   </si>
   <si>
     <t>Straw added 30+ days pre cultivation (t/ha)</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Data quality scoring</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_TemporalRepresentativeness</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Data collected covers the time-period for which emissions are being estimated  </t>
+  </si>
+  <si>
+    <t>TR5</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 2 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR4</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 3 years of to the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Data collected represents activities that occurred within 4 years of the time-period being assessed  </t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>Age of data unknown or data more than 4 years older than the time-period being reported  </t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SpatialRepresentativeness</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) with spatial partitioning or using stratified sampling within property </t>
+  </si>
+  <si>
+    <t>SR5</t>
+  </si>
+  <si>
+    <t>Data covers specific entity location(s) without spatial partitioning within property  </t>
+  </si>
+  <si>
+    <t>SR4</t>
+  </si>
+  <si>
+    <t>Data based on regional data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR3</t>
+  </si>
+  <si>
+    <t>Data based on state data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR2</t>
+  </si>
+  <si>
+    <t>Data based on national data from a government or industry database or survey </t>
+  </si>
+  <si>
+    <t>SR1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_SampleSize</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &gt;90% (e.g. total annual fuel purchases) </t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 51-90%  </t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>Data based on sample size of 21-50%  </t>
+  </si>
+  <si>
+    <t>SS3</t>
+  </si>
+  <si>
+    <t>Data based on sample size of &lt;20% (e.g. liveweight measured for 10% of herd) </t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>Unknown (e.g. data based on national/state/regional data source) </t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>Table_SourceData_DataQuality_Scope3</t>
+  </si>
+  <si>
+    <t>Verified data provided by supplier consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard </t>
+  </si>
+  <si>
+    <t>S35</t>
+  </si>
+  <si>
+    <t>Unverified supplier data, consistent with ISO14067:2018 or GHG Protocol Product Lifecycle Accounting and Reporting Standard, or consistent with these Guidelines (where appropriate)</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Regionally relevant product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S33</t>
+  </si>
+  <si>
+    <t>Nationally relevant product specific value from database developed using international best practice   </t>
+  </si>
+  <si>
+    <t>S32</t>
+  </si>
+  <si>
+    <t>Geographically generic product specific value from database developed using international best practice </t>
+  </si>
+  <si>
+    <t>S31</t>
   </si>
 </sst>
 </file>
@@ -1960,7 +2131,7 @@
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2288,6 +2459,7 @@
     <xf numFmtId="0" fontId="63" fillId="9" borderId="5" xfId="36" applyFont="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="34"/>
   </cellXfs>
   <cellStyles count="70">
     <cellStyle name="Alert" xfId="62" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2361,7 +2533,7 @@
     <cellStyle name="Variable type input" xfId="65" xr:uid="{83ED2376-8555-47B3-98E3-2416CC880284}"/>
     <cellStyle name="Variable type other" xfId="66" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="67">
     <dxf>
       <font>
         <color rgb="FFC44340"/>
@@ -2479,6 +2651,30 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3692,20 +3888,20 @@
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Equation table" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Editable table" pivot="0" count="6" xr9:uid="{8C498A1C-5864-4BF8-8739-A3055FE117E0}">
-      <tableStyleElement type="wholeTable" dxfId="65"/>
-      <tableStyleElement type="headerRow" dxfId="64"/>
-      <tableStyleElement type="totalRow" dxfId="63"/>
-      <tableStyleElement type="firstColumn" dxfId="62"/>
-      <tableStyleElement type="firstRowStripe" dxfId="61"/>
-      <tableStyleElement type="secondRowStripe" dxfId="60"/>
+      <tableStyleElement type="wholeTable" dxfId="66"/>
+      <tableStyleElement type="headerRow" dxfId="65"/>
+      <tableStyleElement type="totalRow" dxfId="64"/>
+      <tableStyleElement type="firstColumn" dxfId="63"/>
+      <tableStyleElement type="firstRowStripe" dxfId="62"/>
+      <tableStyleElement type="secondRowStripe" dxfId="61"/>
     </tableStyle>
     <tableStyle name="Equation table" pivot="0" count="6" xr9:uid="{B247698E-E41D-4CCD-AA0A-C14817E9DE65}">
-      <tableStyleElement type="wholeTable" dxfId="59"/>
-      <tableStyleElement type="headerRow" dxfId="58"/>
-      <tableStyleElement type="totalRow" dxfId="57"/>
-      <tableStyleElement type="firstColumn" dxfId="56"/>
-      <tableStyleElement type="firstRowStripe" dxfId="55"/>
-      <tableStyleElement type="secondRowStripe" dxfId="54"/>
+      <tableStyleElement type="wholeTable" dxfId="60"/>
+      <tableStyleElement type="headerRow" dxfId="59"/>
+      <tableStyleElement type="totalRow" dxfId="58"/>
+      <tableStyleElement type="firstColumn" dxfId="57"/>
+      <tableStyleElement type="firstRowStripe" dxfId="56"/>
+      <tableStyleElement type="secondRowStripe" dxfId="55"/>
     </tableStyle>
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{97B370DB-5463-4A31-9160-5A96BD6A559D}"/>
   </tableStyles>
@@ -7123,12 +7319,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3F57B357-DC08-4E9D-B447-EFDAB703AC98}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CFBBECF9-87C0-414D-87BB-FB2F5EE27B45}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{0B059BCA-C44D-447F-BDC2-14E641A01924}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{88B560B1-34F3-4BDE-88F8-0943DCF1CD98}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7137,16 +7333,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FD6D0F6-61EF-4B3E-B946-4BEFCDD6906C}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{7887A690-69D3-425C-9152-99C4B62008CB}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FBEBA280-A8EC-44D0-BE88-CE2C1D3B3DDD}" name="Gas">
+    <tableColumn id="1" xr3:uid="{0670A52C-4D72-4FF3-9999-DC9B94C0761F}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{171DA041-A357-41AC-A814-8C797D3F7502}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{1AAD72E9-1A9D-4CAA-AF3C-8A8F49D892B3}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7155,7 +7351,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{11AF29CC-97F2-488B-9F8A-EE1953F18328}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{34DC17E8-6104-43A3-9CCA-C22597C5C535}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7164,19 +7360,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{CE4DDF8F-C229-4BA5-B737-9F2513BCCB80}" name="Gas">
+    <tableColumn id="1" xr3:uid="{96DFB5FF-FB12-4A61-AE69-FFA146252AD4}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{1E77BC4D-AF1C-49A1-B818-655E663524F1}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{C8D4CA51-2241-4E24-BAF4-1372490A0C52}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6D856132-4FAF-467C-BF04-4A1B4E569EAA}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{77535BE4-0A0D-4020-AC84-CF648B461848}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C65DF7A8-FE65-4A5D-A04B-3FA2682FF346}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{5BAA3F96-2C12-4284-9FCA-CC9F0D42A63A}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3AE7AC1-A079-4CE1-886E-B0A550DFAE07}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{CAB9D796-F451-4166-9315-13E0513C6CD7}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7185,7 +7381,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5966959C-8843-43C3-9FFB-A5D69543C0B3}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{14F960DC-9541-486F-B402-5D7CEBFAE490}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7205,52 +7401,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F2B28D50-A034-4DB4-A490-A64A9E8A5482}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{EF806262-B893-4201-911D-B72CD3C92E38}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A2505FF3-32B5-4C99-ABA7-5BA255B37323}" name="MAT" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{C564F362-C377-4943-B09E-17512BBEA4C1}" name="MAT" totalsRowDxfId="54" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E3B96E6B-F316-4EEC-9D7F-009294682D91}" name="MAP" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{270E921A-D34F-4D86-B2E1-D43B6F3C8D8F}" name="MAP" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{68BEE58B-963F-47BB-B1B5-A522D3A5C53A}" name="Frost days per year" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{CCF02364-47E2-43EE-A412-D52A13B1843A}" name="Frost days per year" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F8A437EF-EB5A-4EC8-B505-D4618F05DEC8}" name="Elevation" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EA942902-878A-4B0A-8DBA-043EB49B0389}" name="Elevation" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{45310AA7-5B2C-42B7-9B25-A9FB5D140114}" name="MAP:PET" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{27D4BA15-4E10-4C61-98F9-5E6DF7EC8AA1}" name="MAP:PET" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A5AACB52-18FB-4666-A3C5-6B1E42CA013B}" name="Min temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{D4ED479A-7096-4C11-9053-2907063106F3}" name="Min temp" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{578AA7B3-4FC1-4500-8566-45FFD6554344}" name="Max temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{141BCFA1-6703-47A0-913A-4EDEBB01241B}" name="Max temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{71E728CB-79BC-4EBB-B382-57BA8BEBAF42}" name="Min rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{278A32E9-3374-43B7-B6CE-1D808647E5EF}" name="Min rainfall" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{3639C603-3EA1-4589-968F-24F11750C017}" name="Max rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{30B1D4E1-AAE4-4236-85AC-BEF51FFF332C}" name="Max rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{B3831A0E-57C9-4EBE-BC45-06FC3AC17059}" name="Min frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{67D3F552-DF5E-4472-A592-12D7C1C2A0C2}" name="Min frost days" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{DE298B36-E53A-48C8-85EC-797D8AB410D0}" name="Max frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BC2EC11C-30F7-450C-B4FE-B72E9E6F20E1}" name="Max frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{5869E771-1803-4855-88C0-38872F74AB77}" name="Min elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{FFED5AC9-47ED-46D9-9F65-9A7111D2670F}" name="Min elevation" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{73B45490-B776-47F2-B880-734E845FD77D}" name="Max elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{97F34A81-C6B6-4BCF-A8B7-5B81E8FBAC73}" name="Max elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{43F6550D-5E97-414A-8F2E-088DAAC56A72}" name="Min MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{F5DE89C6-153D-4836-9F6C-7082285CEB7E}" name="Min MAP:PET" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DF3BC22B-D7AD-4013-87AA-B3C2C846F823}" name="Max MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{337EB6FA-7C02-44B1-824F-BA56C5F6229A}" name="Max MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7259,16 +7455,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{53D3DFA8-2A0F-4293-BA50-6A987BF486DF}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{B1C188FF-68BF-4676-9F1F-EEE27C109412}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FFEC2A23-B63B-498B-A95F-E25594074A8B}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{4CEC61E2-AC3E-41EE-A75F-075546A5CD0C}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F6E1E0AA-E22E-4A1C-953F-44360B524662}" name="Wet or Dry Zone" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{B7CF3A8C-8632-43C9-AC0A-06F7BA5FD1C8}" name="Wet or Dry Zone" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7277,7 +7473,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{3DA56B25-EFD6-4760-BF63-A8F7647724EF}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{5AB7F1D6-4140-4C7B-85E9-EA394241F29F}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7285,16 +7481,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{93A3B1A1-71C3-4FCF-95BA-81F6467E852B}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{45862E05-CA51-4C60-9B8A-AB1F7A6483F7}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1A91D15F-0988-42FF-BE84-EF2E8460E896}" name="MAT">
+    <tableColumn id="2" xr3:uid="{C6A4311B-39D7-45A2-A0AD-5B2BAD3E4B29}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{CAE683C2-8E2C-43C4-B23E-B4C650D9CFC9}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{34E02F55-E1C9-4F3E-849C-63C798C91934}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{62F6DF8F-E35A-4469-AE17-F85F0E02A736}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{947EDF2E-64C2-4458-9673-B66DE575671A}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7303,7 +7499,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4F59F7E3-F5EA-4FEB-917F-3B66BB81CF43}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{859765AE-60B7-4A9E-8087-3D819E425B30}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7311,16 +7507,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D6E2C7E2-A0D0-4F22-87FC-81D8B123DAF1}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{67636B01-73D3-4862-96BD-C2DF1AB56303}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{29F247EC-D1DC-4C40-91DE-FC0D10878593}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{DDA8D18E-00F7-401E-AE0D-712E98D9F686}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B4E77F9A-F815-4886-AA6C-48BECBB05314}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{99759B09-C731-4350-AB16-E9FBED3F4D28}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A788A069-55B8-4418-A9F5-7C05D4FC2A84}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{C0666FAF-D435-437A-BB21-2592FB0FF6FE}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7329,16 +7525,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{2BADACA7-8B14-4DD0-A496-EAC6B5672909}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{1842FFEF-E61E-4BA0-8168-C77294C73BEC}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0A2C56F0-13CC-42C1-BA02-30776F544A00}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{4DAF6728-9997-441D-A802-BF87DDC89101}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0F954C7-9A1E-469C-9772-C1D30F16621F}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{F8F88980-3E04-4C1C-A652-0F4B6FBC0B6B}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7347,16 +7543,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{A4DA27C6-2B10-42E9-B61C-9BBB344FC969}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{E03E94EB-A69E-4046-8B6E-75835A826AB0}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F7666537-6ED5-4031-8ECB-23C9AEDC45D3}" name="Data source">
+    <tableColumn id="1" xr3:uid="{7E5DED90-ED93-4AEE-8DA8-FBE0D8E38943}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0BC5AFBF-2F3A-45AC-B785-08479E59FFDA}" name="Data score">
+    <tableColumn id="2" xr3:uid="{0CCA883A-2CB1-4D33-B2C0-6BE6C0E20C37}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7365,16 +7561,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{E2DEE321-B337-4BC8-9070-167098B674D5}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{91295A96-8B22-40C3-9464-8C386B337458}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DBB178F3-4169-471E-9922-C17C5F637499}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{530BD565-59A2-434D-8357-04A0A75FC23B}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F3628DE2-FAFC-4288-AFB2-812352B720BC}" name="FracWET" dataDxfId="37">
+    <tableColumn id="2" xr3:uid="{55DDB931-6387-45EC-966A-047FF2101652}" name="FracWET" dataDxfId="38">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7407,7 +7603,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7D8156AA-47C5-4304-997D-5EF3F53749EE}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{5AF0B56A-6DAC-459F-BA8D-A617FBD7C405}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7416,19 +7612,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{0C4D37B5-F284-4EBD-B8A3-CFDDD667EB11}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{9940F398-4403-4AF7-8972-EE0B7B3CE1DD}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFC1262B-E8CB-4898-8D52-FD08482C885C}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{0FA8325A-177E-4D59-9FE0-6B903853CD18}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5A13419B-46E6-47C3-A0AA-0BEDECD2A1D1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{0EEC98F2-3796-4F27-AF04-9C27AD5F94EC}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{392B1761-2983-4CA2-8BE7-A6C347E20451}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{8622D985-353B-44B3-B3F3-6294BBBB774C}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4FA3A003-D7B5-4095-9AAD-E1B03BAFA23C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{9C8C2026-E422-40D1-B7A8-E05A246CEC28}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7437,16 +7633,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{FDEC7E83-8E36-4A31-B7A7-690E1AAC31B5}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{AD9C104E-1F4A-415F-B7F5-A4146B1D279E}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETI